--- a/設定ファイル/静止画_60us/静止画_60us_CLK1.xlsx
+++ b/設定ファイル/静止画_60us/静止画_60us_CLK1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e12206\GitHub\DCDC_clock_simulator\設定ファイル\静止画_60us\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEAAA46-3B00-4041-B36F-3FCF01A1CA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA533AF-8B87-41C3-92E0-75FE5559E70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4150" yWindow="0" windowWidth="14550" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
@@ -717,7 +717,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2">
-        <v>31.15</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -725,7 +725,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="2">
-        <v>37.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -733,7 +733,7 @@
         <v>36</v>
       </c>
       <c r="B23" s="2">
-        <v>8.15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -741,7 +741,7 @@
         <v>37</v>
       </c>
       <c r="B24" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -749,7 +749,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2">
-        <v>10.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -775,7 +775,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="2">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -791,7 +791,7 @@
         <v>44</v>
       </c>
       <c r="B31" s="2">
-        <v>16.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
